--- a/Клиенты_страхование_ТЕСТ.xlsx
+++ b/Клиенты_страхование_ТЕСТ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masha\Desktop\Страхование_Банкротство\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masha\Documents\fedresurs-bankruptcy-monitor-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FC471A-EC85-4C8F-8E07-41D17115CC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29319B40-5F6E-43C4-A275-8E3FFA5C7556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="-108" windowWidth="21768" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">Наименование Контрагента </t>
   </si>
@@ -56,168 +56,6 @@
   </si>
   <si>
     <t>ООО "СТАР ИНТЕГРАЦИЯ"</t>
-  </si>
-  <si>
-    <t>ООО "РИС"</t>
-  </si>
-  <si>
-    <t>ООО "АЛЬЯНС"</t>
-  </si>
-  <si>
-    <t>ООО "АКСАИС"</t>
-  </si>
-  <si>
-    <t>ООО "ЦСТБИ"</t>
-  </si>
-  <si>
-    <t>ООО "МОБИРИК"</t>
-  </si>
-  <si>
-    <t>ООО "МАТРЕШКА"</t>
-  </si>
-  <si>
-    <t>АО "РОТОР"</t>
-  </si>
-  <si>
-    <t>ОАО "АВТОРЕМСАЛОН"</t>
-  </si>
-  <si>
-    <t>АО "ТАГАНРОГСКАЯ ПМК "РСВС"</t>
-  </si>
-  <si>
-    <t>ОАО "ЗАПСИБАГРОПРОМСПЕЦПРОЕКТ"</t>
-  </si>
-  <si>
-    <t>ОАО "ВК СРЗ"</t>
-  </si>
-  <si>
-    <t>ОАО " ДАГЕСТАНГЕОЛОГИЯ "</t>
-  </si>
-  <si>
-    <t>ОАО "ТСП СТРОЙМАТЕРИАЛЫ"</t>
-  </si>
-  <si>
-    <t>ОАО "ДОРОЖНИК"</t>
-  </si>
-  <si>
-    <t>АО "УМ САРАТОВАВТОДОР"</t>
-  </si>
-  <si>
-    <t>ОАО УПКИТ "ПРОФЕССИОНАЛ"</t>
-  </si>
-  <si>
-    <t>ООО "АННИНО-С"</t>
-  </si>
-  <si>
-    <t>ООО "АЛЬТ"</t>
-  </si>
-  <si>
-    <t>ООО "АПТЕКА-САЛЬВЕ"</t>
-  </si>
-  <si>
-    <t>ООО "АКАИ"</t>
-  </si>
-  <si>
-    <t>ООО "АДМ"</t>
-  </si>
-  <si>
-    <t>ООО "АЛИ"</t>
-  </si>
-  <si>
-    <t>ООО "АЛМАЗ-РИ"</t>
-  </si>
-  <si>
-    <t>ООО "АНТИС"</t>
-  </si>
-  <si>
-    <t>ООО "АДАМАНТ"</t>
-  </si>
-  <si>
-    <t>ООО "Русавтоснаб"</t>
-  </si>
-  <si>
-    <t>ООО "Русбиофарма"</t>
-  </si>
-  <si>
-    <t>ООО «РУСГЕОКОМ»</t>
-  </si>
-  <si>
-    <t>ООО "Русдорзнак"</t>
-  </si>
-  <si>
-    <t>ООО «РУСИНТЕРМЕД»</t>
-  </si>
-  <si>
-    <t>ООО "Русич"</t>
-  </si>
-  <si>
-    <t>ООО "РУСКОМП"</t>
-  </si>
-  <si>
-    <t>ООО "РУСОКНО"</t>
-  </si>
-  <si>
-    <t>ООО «РУСОФАРМ»</t>
-  </si>
-  <si>
-    <t>ООО "Русское слово-учебник"</t>
-  </si>
-  <si>
-    <t>ООО "Руссторг"</t>
-  </si>
-  <si>
-    <t>ООО "СУРИКАТ"</t>
-  </si>
-  <si>
-    <t>ООО "СУТОРМИНА"</t>
-  </si>
-  <si>
-    <t>ООО "СФЕРА"</t>
-  </si>
-  <si>
-    <t>ООО "СЭИЛ ФАКТОРИ"</t>
-  </si>
-  <si>
-    <t>ООО "СЭЙЛГУД"</t>
-  </si>
-  <si>
-    <t>ООО "СЭМ"</t>
-  </si>
-  <si>
-    <t>ООО "ЗАПСИБНЕФТЕХИМ"</t>
-  </si>
-  <si>
-    <t>ООО "СПАР МИДДЛ ВОЛГА"</t>
-  </si>
-  <si>
-    <t>ООО "РН-ЭНЕРГО"</t>
-  </si>
-  <si>
-    <t>АО "ФГК"</t>
-  </si>
-  <si>
-    <t>ООО "ГАЗПРОМ ДОБЫЧА АСТРАХАНЬ"</t>
-  </si>
-  <si>
-    <t>АО "ТБанк"</t>
-  </si>
-  <si>
-    <t>АО "Страховое общество газовой промышленности"</t>
-  </si>
-  <si>
-    <t>АО "РТКомм.РУ"</t>
-  </si>
-  <si>
-    <t>АО "Производственная фирма "СКБ Контур"</t>
-  </si>
-  <si>
-    <t>АО "Папилон"</t>
-  </si>
-  <si>
-    <t>АО "Ильмен-Тау"</t>
-  </si>
-  <si>
-    <t>АО "Издательство "Просвещение"</t>
   </si>
 </sst>
 </file>
@@ -380,6 +218,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -392,7 +231,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -688,20 +526,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
@@ -712,14 +550,14 @@
       <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="6" spans="1:6" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -742,7 +580,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2">
@@ -754,7 +592,7 @@
       <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2">
@@ -766,7 +604,7 @@
       <c r="F8" s="11"/>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2">
@@ -778,648 +616,432 @@
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2">
-        <v>7813647559</v>
-      </c>
+      <c r="A10" s="17"/>
+      <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
       <c r="E10" s="5"/>
       <c r="F10" s="11"/>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2">
-        <v>6685138424</v>
-      </c>
+      <c r="A11" s="17"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
       <c r="E11" s="5"/>
       <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2">
-        <v>9701186712</v>
-      </c>
+      <c r="A12" s="17"/>
+      <c r="B12" s="2"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
       <c r="E12" s="5"/>
       <c r="F12" s="11"/>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2">
-        <v>7713691508</v>
-      </c>
+      <c r="A13" s="17"/>
+      <c r="B13" s="2"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
       <c r="E13" s="5"/>
       <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2">
-        <v>5902047849</v>
-      </c>
+      <c r="A14" s="17"/>
+      <c r="B14" s="2"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
       <c r="E14" s="5"/>
       <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2">
-        <v>9701102110</v>
-      </c>
+      <c r="A15" s="17"/>
+      <c r="B15" s="2"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
       <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3525078725</v>
-      </c>
+      <c r="A16" s="17"/>
+      <c r="B16" s="2"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
       <c r="E16" s="5"/>
       <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2">
-        <v>7020030013</v>
-      </c>
+      <c r="A17" s="17"/>
+      <c r="B17" s="2"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
       <c r="E17" s="5"/>
       <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="2">
-        <v>6123001460</v>
-      </c>
+      <c r="A18" s="17"/>
+      <c r="B18" s="2"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
       <c r="E18" s="5"/>
       <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="2">
-        <v>5405106565</v>
-      </c>
+      <c r="A19" s="17"/>
+      <c r="B19" s="2"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5"/>
       <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="2">
-        <v>3005000602</v>
-      </c>
+      <c r="A20" s="17"/>
+      <c r="B20" s="2"/>
       <c r="C20" s="3"/>
       <c r="D20" s="4"/>
       <c r="E20" s="5"/>
       <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="2">
-        <v>561019825</v>
-      </c>
+      <c r="A21" s="17"/>
+      <c r="B21" s="2"/>
       <c r="C21" s="3"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5"/>
       <c r="F21" s="11"/>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="2">
-        <v>2636025766</v>
-      </c>
+      <c r="A22" s="17"/>
+      <c r="B22" s="2"/>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
       <c r="E22" s="5"/>
       <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="2">
-        <v>6224002397</v>
-      </c>
+      <c r="A23" s="17"/>
+      <c r="B23" s="2"/>
       <c r="C23" s="3"/>
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
       <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="2">
-        <v>6432006547</v>
-      </c>
+      <c r="A24" s="17"/>
+      <c r="B24" s="2"/>
       <c r="C24" s="3"/>
       <c r="D24" s="4"/>
       <c r="E24" s="5"/>
       <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2">
-        <v>7736161190</v>
-      </c>
+      <c r="A25" s="17"/>
+      <c r="B25" s="2"/>
       <c r="C25" s="3"/>
       <c r="D25" s="4"/>
       <c r="E25" s="5"/>
       <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="2">
-        <v>7726070353</v>
-      </c>
+      <c r="A26" s="17"/>
+      <c r="B26" s="2"/>
       <c r="C26" s="3"/>
       <c r="D26" s="4"/>
       <c r="E26" s="5"/>
       <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="2">
-        <v>7721007189</v>
-      </c>
+      <c r="A27" s="17"/>
+      <c r="B27" s="2"/>
       <c r="C27" s="3"/>
       <c r="D27" s="4"/>
       <c r="E27" s="5"/>
       <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="2">
-        <v>7713022803</v>
-      </c>
+      <c r="A28" s="17"/>
+      <c r="B28" s="2"/>
       <c r="C28" s="3"/>
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
       <c r="F28" s="11"/>
     </row>
     <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="2">
-        <v>7743000187</v>
-      </c>
+      <c r="A29" s="17"/>
+      <c r="B29" s="2"/>
       <c r="C29" s="3"/>
       <c r="D29" s="4"/>
       <c r="E29" s="5"/>
       <c r="F29" s="11"/>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="2">
-        <v>7715017679</v>
-      </c>
+      <c r="A30" s="17"/>
+      <c r="B30" s="2"/>
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
       <c r="E30" s="5"/>
       <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="2">
-        <v>7728187741</v>
-      </c>
+      <c r="A31" s="17"/>
+      <c r="B31" s="2"/>
       <c r="C31" s="3"/>
       <c r="D31" s="4"/>
       <c r="E31" s="5"/>
       <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="2">
-        <v>7705044088</v>
-      </c>
+      <c r="A32" s="17"/>
+      <c r="B32" s="2"/>
       <c r="C32" s="3"/>
       <c r="D32" s="4"/>
       <c r="E32" s="5"/>
       <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="2">
-        <v>7722008820</v>
-      </c>
+      <c r="A33" s="17"/>
+      <c r="B33" s="2"/>
       <c r="C33" s="3"/>
       <c r="D33" s="4"/>
       <c r="E33" s="5"/>
       <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="2">
-        <v>7725018600</v>
-      </c>
+      <c r="A34" s="17"/>
+      <c r="B34" s="2"/>
       <c r="C34" s="3"/>
       <c r="D34" s="4"/>
       <c r="E34" s="5"/>
       <c r="F34" s="11"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" s="2">
-        <v>7710140679</v>
-      </c>
+      <c r="A35" s="17"/>
+      <c r="B35" s="2"/>
       <c r="C35" s="3"/>
       <c r="D35" s="4"/>
       <c r="E35" s="5"/>
       <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B36" s="2">
-        <v>7736035485</v>
-      </c>
+      <c r="A36" s="17"/>
+      <c r="B36" s="2"/>
       <c r="C36" s="3"/>
       <c r="D36" s="4"/>
       <c r="E36" s="5"/>
       <c r="F36" s="11"/>
     </row>
     <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" s="2">
-        <v>7708126998</v>
-      </c>
+      <c r="A37" s="17"/>
+      <c r="B37" s="2"/>
       <c r="C37" s="3"/>
       <c r="D37" s="4"/>
       <c r="E37" s="5"/>
       <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" s="2">
-        <v>6663003127</v>
-      </c>
+      <c r="A38" s="17"/>
+      <c r="B38" s="2"/>
       <c r="C38" s="3"/>
       <c r="D38" s="4"/>
       <c r="E38" s="5"/>
       <c r="F38" s="11"/>
     </row>
     <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" s="2">
-        <v>7415020254</v>
-      </c>
+      <c r="A39" s="17"/>
+      <c r="B39" s="2"/>
       <c r="C39" s="3"/>
       <c r="D39" s="4"/>
       <c r="E39" s="5"/>
       <c r="F39" s="11"/>
     </row>
     <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" s="2">
-        <v>7415054542</v>
-      </c>
+      <c r="A40" s="17"/>
+      <c r="B40" s="2"/>
       <c r="C40" s="3"/>
       <c r="D40" s="4"/>
       <c r="E40" s="5"/>
       <c r="F40" s="11"/>
     </row>
     <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" s="2">
-        <v>7715995942</v>
-      </c>
+      <c r="A41" s="17"/>
+      <c r="B41" s="2"/>
       <c r="C41" s="3"/>
       <c r="D41" s="4"/>
       <c r="E41" s="5"/>
       <c r="F41" s="11"/>
     </row>
     <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" s="2">
-        <v>5837079407</v>
-      </c>
+      <c r="A42" s="17"/>
+      <c r="B42" s="2"/>
       <c r="C42" s="3"/>
       <c r="D42" s="4"/>
       <c r="E42" s="5"/>
       <c r="F42" s="11"/>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B43" s="2">
-        <v>4633036361</v>
-      </c>
+      <c r="A43" s="17"/>
+      <c r="B43" s="2"/>
       <c r="C43" s="3"/>
       <c r="D43" s="4"/>
       <c r="E43" s="5"/>
       <c r="F43" s="11"/>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="2">
-        <v>7716540377</v>
-      </c>
+      <c r="A44" s="17"/>
+      <c r="B44" s="2"/>
       <c r="C44" s="3"/>
       <c r="D44" s="4"/>
       <c r="E44" s="5"/>
       <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="2">
-        <v>6453143209</v>
-      </c>
+      <c r="A45" s="17"/>
+      <c r="B45" s="2"/>
       <c r="C45" s="3"/>
       <c r="D45" s="4"/>
       <c r="E45" s="5"/>
       <c r="F45" s="11"/>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="2">
-        <v>5252011899</v>
-      </c>
+      <c r="A46" s="17"/>
+      <c r="B46" s="2"/>
       <c r="C46" s="3"/>
       <c r="D46" s="4"/>
       <c r="E46" s="5"/>
       <c r="F46" s="11"/>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="2">
-        <v>5837055879</v>
-      </c>
+      <c r="A47" s="17"/>
+      <c r="B47" s="2"/>
       <c r="C47" s="3"/>
       <c r="D47" s="4"/>
       <c r="E47" s="5"/>
       <c r="F47" s="11"/>
     </row>
     <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="2">
-        <v>5835085162</v>
-      </c>
+      <c r="A48" s="17"/>
+      <c r="B48" s="2"/>
       <c r="C48" s="3"/>
       <c r="D48" s="4"/>
       <c r="E48" s="5"/>
       <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="2">
-        <v>5836694470</v>
-      </c>
+      <c r="A49" s="17"/>
+      <c r="B49" s="2"/>
       <c r="C49" s="3"/>
       <c r="D49" s="4"/>
       <c r="E49" s="5"/>
       <c r="F49" s="11"/>
     </row>
     <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="2">
-        <v>7727419284</v>
-      </c>
+      <c r="A50" s="17"/>
+      <c r="B50" s="2"/>
       <c r="C50" s="3"/>
       <c r="D50" s="4"/>
       <c r="E50" s="5"/>
       <c r="F50" s="11"/>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="2">
-        <v>7729656731</v>
-      </c>
+      <c r="A51" s="17"/>
+      <c r="B51" s="2"/>
       <c r="C51" s="3"/>
       <c r="D51" s="4"/>
       <c r="E51" s="5"/>
       <c r="F51" s="11"/>
     </row>
     <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="2">
-        <v>5835129028</v>
-      </c>
+      <c r="A52" s="17"/>
+      <c r="B52" s="2"/>
       <c r="C52" s="3"/>
       <c r="D52" s="4"/>
       <c r="E52" s="5"/>
       <c r="F52" s="11"/>
     </row>
     <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="2">
-        <v>5027328694</v>
-      </c>
+      <c r="A53" s="17"/>
+      <c r="B53" s="2"/>
       <c r="C53" s="3"/>
       <c r="D53" s="4"/>
       <c r="E53" s="5"/>
       <c r="F53" s="11"/>
     </row>
     <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B54" s="2">
-        <v>5032393917</v>
-      </c>
+      <c r="A54" s="17"/>
+      <c r="B54" s="2"/>
       <c r="C54" s="3"/>
       <c r="D54" s="4"/>
       <c r="E54" s="5"/>
       <c r="F54" s="11"/>
     </row>
     <row r="55" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="B55" s="2">
-        <v>5012098536</v>
-      </c>
+      <c r="A55" s="17"/>
+      <c r="B55" s="2"/>
       <c r="C55" s="3"/>
       <c r="D55" s="4"/>
       <c r="E55" s="5"/>
       <c r="F55" s="11"/>
     </row>
     <row r="56" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56" s="2">
-        <v>5047248158</v>
-      </c>
+      <c r="A56" s="17"/>
+      <c r="B56" s="2"/>
       <c r="C56" s="3"/>
       <c r="D56" s="4"/>
       <c r="E56" s="5"/>
       <c r="F56" s="11"/>
     </row>
     <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B57" s="2">
-        <v>5043075120</v>
-      </c>
+      <c r="A57" s="17"/>
+      <c r="B57" s="2"/>
       <c r="C57" s="3"/>
       <c r="D57" s="4"/>
       <c r="E57" s="5"/>
       <c r="F57" s="11"/>
     </row>
     <row r="58" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B58" s="2">
-        <v>5044145267</v>
-      </c>
+      <c r="A58" s="17"/>
+      <c r="B58" s="2"/>
       <c r="C58" s="3"/>
       <c r="D58" s="4"/>
       <c r="E58" s="5"/>
       <c r="F58" s="11"/>
     </row>
     <row r="59" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59" s="2">
-        <v>1658087524</v>
-      </c>
+      <c r="A59" s="17"/>
+      <c r="B59" s="2"/>
       <c r="C59" s="3"/>
       <c r="D59" s="4"/>
       <c r="E59" s="5"/>
       <c r="F59" s="11"/>
     </row>
     <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" s="2">
-        <v>5258056945</v>
-      </c>
+      <c r="A60" s="17"/>
+      <c r="B60" s="2"/>
       <c r="C60" s="3"/>
       <c r="D60" s="4"/>
       <c r="E60" s="5"/>
       <c r="F60" s="11"/>
     </row>
     <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B61" s="2">
-        <v>7706525041</v>
-      </c>
+      <c r="A61" s="17"/>
+      <c r="B61" s="2"/>
       <c r="C61" s="3"/>
       <c r="D61" s="4"/>
       <c r="E61" s="5"/>
       <c r="F61" s="11"/>
     </row>
     <row r="62" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62" s="2">
-        <v>6659209750</v>
-      </c>
+      <c r="A62" s="17"/>
+      <c r="B62" s="2"/>
       <c r="C62" s="3"/>
       <c r="D62" s="4"/>
       <c r="E62" s="5"/>
       <c r="F62" s="11"/>
     </row>
     <row r="63" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" s="2">
-        <v>3006006420</v>
-      </c>
+      <c r="A63" s="17"/>
+      <c r="B63" s="2"/>
       <c r="C63" s="3"/>
       <c r="D63" s="4"/>
       <c r="E63" s="5"/>
@@ -1428,23 +1050,23 @@
     <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
       <c r="B67" s="9"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="18"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
@@ -1464,15 +1086,15 @@
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
     </row>
     <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="6"/>
       <c r="D74" s="6"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="17"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/Клиенты_страхование_ТЕСТ.xlsx
+++ b/Клиенты_страхование_ТЕСТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masha\Documents\fedresurs-bankruptcy-monitor-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29319B40-5F6E-43C4-A275-8E3FFA5C7556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B7E7D3D-8AF1-4C48-8F59-939762DF4A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="-108" windowWidth="21768" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">Наименование Контрагента </t>
   </si>
@@ -57,6 +57,12 @@
   <si>
     <t>ООО "СТАР ИНТЕГРАЦИЯ"</t>
   </si>
+  <si>
+    <t>ПАО "ЮГК"</t>
+  </si>
+  <si>
+    <t>АО "БЕАТОН"</t>
+  </si>
 </sst>
 </file>
 
@@ -66,7 +72,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +121,20 @@
       <sz val="10"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -168,7 +188,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -230,6 +250,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -579,8 +603,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2">
@@ -591,8 +615,8 @@
       <c r="E7" s="5"/>
       <c r="F7" s="11"/>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2">
@@ -603,8 +627,8 @@
       <c r="E8" s="5"/>
       <c r="F8" s="11"/>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2">
@@ -615,17 +639,25 @@
       <c r="E9" s="5"/>
       <c r="F9" s="11"/>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="17"/>
-      <c r="B10" s="2"/>
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2">
+        <v>7424024375</v>
+      </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
       <c r="E10" s="5"/>
       <c r="F10" s="11"/>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17"/>
-      <c r="B11" s="2"/>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2">
+        <v>7825367884</v>
+      </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
       <c r="E11" s="5"/>
